--- a/MCU_Fault/MCU_FaultDiag_Datadictionary.xlsx
+++ b/MCU_Fault/MCU_FaultDiag_Datadictionary.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="12400" activeTab="2"/>
+    <workbookView windowWidth="12390" windowHeight="5400" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="History" sheetId="5" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="322">
   <si>
     <t>Version</t>
   </si>
@@ -892,6 +892,27 @@
   </si>
   <si>
     <t>C_Fault_SelfCheckFaultErrCode_u16</t>
+  </si>
+  <si>
+    <t>C_Fault_CANFaultDiagEn_u8</t>
+  </si>
+  <si>
+    <t>C_Fault_CANFaultLevel_u8</t>
+  </si>
+  <si>
+    <t>C_Fault_CANFaultCoeff_f32</t>
+  </si>
+  <si>
+    <t>C_Fault_CANFaultErrCode_u16</t>
+  </si>
+  <si>
+    <t>C_Fault_CANFaultVehicleCount_u16</t>
+  </si>
+  <si>
+    <t>C_Fault_CANFaultTestbedCount_u16</t>
+  </si>
+  <si>
+    <t>C_Fault_CANFaultAnalogCount_u16</t>
   </si>
   <si>
     <t>C_Fault_IaLimit_s32</t>
@@ -2020,20 +2041,20 @@
     <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2050,14 +2071,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2068,6 +2089,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2081,13 +2105,10 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2422,16 +2443,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="8.85454545454546" style="43" customWidth="1"/>
-    <col min="2" max="2" width="23.2818181818182" style="43" customWidth="1"/>
-    <col min="3" max="3" width="12.8545454545455" style="43" customWidth="1"/>
-    <col min="4" max="4" width="59.8545454545455" style="44" customWidth="1"/>
+    <col min="1" max="1" width="8.85714285714286" style="43" customWidth="1"/>
+    <col min="2" max="2" width="23.2857142857143" style="43" customWidth="1"/>
+    <col min="3" max="3" width="12.8571428571429" style="43" customWidth="1"/>
+    <col min="4" max="4" width="59.8571428571429" style="44" customWidth="1"/>
     <col min="5" max="16384" width="9" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" s="42" customFormat="1" spans="1:4">
+    <row r="1" s="42" customFormat="1" ht="15" spans="1:4">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -2445,7 +2466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="42" customFormat="1" spans="1:4">
+    <row r="2" s="42" customFormat="1" ht="14.25" spans="1:4">
       <c r="A2" s="9" t="s">
         <v>4</v>
       </c>
@@ -2472,18 +2493,18 @@
   <dimension ref="A1:N84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="42.5272727272727" style="9" customWidth="1"/>
-    <col min="2" max="2" width="13.7363636363636" style="9" customWidth="1"/>
-    <col min="3" max="3" width="9.70909090909091" style="9" customWidth="1"/>
+    <col min="1" max="1" width="42.5238095238095" style="9" customWidth="1"/>
+    <col min="2" max="2" width="13.7333333333333" style="9" customWidth="1"/>
+    <col min="3" max="3" width="9.7047619047619" style="9" customWidth="1"/>
     <col min="4" max="4" width="27" style="9" customWidth="1"/>
     <col min="5" max="5" width="14" style="9" customWidth="1"/>
-    <col min="6" max="6" width="18.2818181818182" style="9" customWidth="1"/>
-    <col min="7" max="7" width="26.6909090909091" style="9" customWidth="1"/>
-    <col min="8" max="8" width="24.0363636363636" style="9" customWidth="1"/>
-    <col min="9" max="9" width="38.3090909090909" style="9" customWidth="1"/>
-    <col min="10" max="11" width="7.42727272727273" style="9" customWidth="1"/>
-    <col min="12" max="12" width="7.13636363636364" style="33" customWidth="1"/>
-    <col min="13" max="14" width="15.4272727272727" style="9" customWidth="1"/>
+    <col min="6" max="6" width="18.2857142857143" style="9" customWidth="1"/>
+    <col min="7" max="7" width="26.6952380952381" style="9" customWidth="1"/>
+    <col min="8" max="8" width="24.0380952380952" style="9" customWidth="1"/>
+    <col min="9" max="9" width="38.3047619047619" style="9" customWidth="1"/>
+    <col min="10" max="11" width="7.42857142857143" style="9" customWidth="1"/>
+    <col min="12" max="12" width="7.13333333333333" style="33" customWidth="1"/>
+    <col min="13" max="14" width="15.4285714285714" style="9" customWidth="1"/>
     <col min="15" max="15" width="9" style="34"/>
     <col min="16" max="16384" width="9" style="9"/>
   </cols>
@@ -2513,7 +2534,7 @@
       <c r="H1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="40" t="s">
+      <c r="I1" s="35" t="s">
         <v>15</v>
       </c>
       <c r="J1" s="17" t="s">
@@ -2532,8 +2553,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:9">
-      <c r="A2" s="35" t="s">
+    <row r="2" customHeight="1" spans="1:14">
+      <c r="A2" s="36" t="s">
         <v>21</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -2561,8 +2582,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:9">
-      <c r="A3" s="35" t="s">
+    <row r="3" customHeight="1" spans="1:14">
+      <c r="A3" s="36" t="s">
         <v>29</v>
       </c>
       <c r="B3" s="9" t="s">
@@ -2590,8 +2611,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:9">
-      <c r="A4" s="35" t="s">
+    <row r="4" customHeight="1" spans="1:14">
+      <c r="A4" s="36" t="s">
         <v>31</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -2620,7 +2641,7 @@
       </c>
     </row>
     <row r="5" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="36" t="s">
         <v>33</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -2645,8 +2666,8 @@
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
-    <row r="7" customHeight="1" spans="1:8">
-      <c r="A7" s="36" t="s">
+    <row r="7" customHeight="1" spans="1:14">
+      <c r="A7" s="37" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -2668,8 +2689,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:8">
-      <c r="A9" s="37" t="s">
+    <row r="9" customHeight="1" spans="1:14">
+      <c r="A9" s="38" t="s">
         <v>36</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -2708,7 +2729,7 @@
       <c r="N10" s="9"/>
     </row>
     <row r="11" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="9" t="s">
@@ -2754,7 +2775,7 @@
       <c r="N12" s="9"/>
     </row>
     <row r="13" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="37" t="s">
         <v>38</v>
       </c>
       <c r="B13" s="9" t="s">
@@ -2800,7 +2821,7 @@
       <c r="N14" s="9"/>
     </row>
     <row r="15" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="38" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="9" t="s">
@@ -2846,7 +2867,7 @@
       <c r="N16" s="9"/>
     </row>
     <row r="17" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="36" t="s">
         <v>40</v>
       </c>
       <c r="B17" s="9" t="s">
@@ -2892,7 +2913,7 @@
       <c r="N18" s="9"/>
     </row>
     <row r="19" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>41</v>
       </c>
       <c r="B19" s="9" t="s">
@@ -2938,7 +2959,7 @@
       <c r="N20" s="9"/>
     </row>
     <row r="21" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="36" t="s">
         <v>42</v>
       </c>
       <c r="B21" s="9" t="s">
@@ -2983,8 +3004,8 @@
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
     </row>
-    <row r="23" customHeight="1" spans="1:9">
-      <c r="A23" s="36" t="s">
+    <row r="23" customHeight="1" spans="1:14">
+      <c r="A23" s="37" t="s">
         <v>43</v>
       </c>
       <c r="B23" s="9" t="s">
@@ -3009,8 +3030,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:9">
-      <c r="A24" s="36" t="s">
+    <row r="24" customHeight="1" spans="1:14">
+      <c r="A24" s="37" t="s">
         <v>45</v>
       </c>
       <c r="B24" s="9" t="s">
@@ -3228,7 +3249,7 @@
       <c r="N36" s="9"/>
     </row>
     <row r="37" s="32" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A37" s="38"/>
+      <c r="A37" s="39"/>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
       <c r="D37" s="15"/>
@@ -3239,12 +3260,12 @@
       <c r="I37" s="15"/>
       <c r="J37" s="15"/>
       <c r="K37" s="15"/>
-      <c r="L37" s="41"/>
+      <c r="L37" s="40"/>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
     </row>
-    <row r="38" customHeight="1" spans="1:8">
-      <c r="A38" s="39" t="s">
+    <row r="38" customHeight="1" spans="1:14">
+      <c r="A38" s="41" t="s">
         <v>47</v>
       </c>
       <c r="B38" s="9" t="s">
@@ -3266,8 +3287,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:8">
-      <c r="A39" s="39" t="s">
+    <row r="39" customHeight="1" spans="1:14">
+      <c r="A39" s="41" t="s">
         <v>50</v>
       </c>
       <c r="B39" s="9" t="s">
@@ -3289,8 +3310,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:8">
-      <c r="A40" s="39" t="s">
+    <row r="40" customHeight="1" spans="1:14">
+      <c r="A40" s="41" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="9" t="s">
@@ -3312,7 +3333,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:9">
+    <row r="44" customHeight="1" spans="1:14">
       <c r="A44" s="9" t="s">
         <v>52</v>
       </c>
@@ -3338,7 +3359,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:9">
+    <row r="47" customHeight="1" spans="1:14">
       <c r="A47" s="9" t="s">
         <v>54</v>
       </c>
@@ -3360,11 +3381,11 @@
       <c r="H47" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I47" s="22" t="s">
+      <c r="I47" s="20" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:9">
+    <row r="48" customHeight="1" spans="1:14">
       <c r="A48" s="9" t="s">
         <v>56</v>
       </c>
@@ -3386,7 +3407,7 @@
       <c r="H48" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I48" s="22" t="s">
+      <c r="I48" s="20" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3412,11 +3433,11 @@
       <c r="H49" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I49" s="22" t="s">
+      <c r="I49" s="20" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:8">
+    <row r="51" customHeight="1" spans="1:9">
       <c r="A51" s="9" t="s">
         <v>60</v>
       </c>
@@ -3439,7 +3460,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:8">
+    <row r="52" customHeight="1" spans="1:9">
       <c r="A52" s="9" t="s">
         <v>61</v>
       </c>
@@ -3462,7 +3483,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="1:8">
+    <row r="53" customHeight="1" spans="1:9">
       <c r="A53" s="9" t="s">
         <v>62</v>
       </c>
@@ -3485,7 +3506,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="1:8">
+    <row r="54" customHeight="1" spans="1:9">
       <c r="A54" s="9" t="s">
         <v>64</v>
       </c>
@@ -3508,7 +3529,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="1:8">
+    <row r="55" customHeight="1" spans="1:9">
       <c r="A55" s="9" t="s">
         <v>66</v>
       </c>
@@ -3531,7 +3552,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="1:8">
+    <row r="56" customHeight="1" spans="1:9">
       <c r="A56" s="9" t="s">
         <v>67</v>
       </c>
@@ -3554,7 +3575,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="1:8">
+    <row r="57" customHeight="1" spans="1:9">
       <c r="A57" s="9" t="s">
         <v>68</v>
       </c>
@@ -3577,7 +3598,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="1:8">
+    <row r="58" customHeight="1" spans="1:9">
       <c r="A58" s="9" t="s">
         <v>70</v>
       </c>
@@ -3600,7 +3621,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="1:8">
+    <row r="59" customHeight="1" spans="1:9">
       <c r="A59" s="9" t="s">
         <v>71</v>
       </c>
@@ -3623,7 +3644,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="1:8">
+    <row r="60" customHeight="1" spans="1:9">
       <c r="A60" s="9" t="s">
         <v>72</v>
       </c>
@@ -3646,7 +3667,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="1:8">
+    <row r="61" customHeight="1" spans="1:9">
       <c r="A61" s="9" t="s">
         <v>73</v>
       </c>
@@ -3669,7 +3690,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="1:8">
+    <row r="62" customHeight="1" spans="1:9">
       <c r="A62" s="9" t="s">
         <v>74</v>
       </c>
@@ -3692,7 +3713,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="1:8">
+    <row r="63" customHeight="1" spans="1:9">
       <c r="A63" s="9" t="s">
         <v>75</v>
       </c>
@@ -4115,23 +4136,23 @@
   <dimension ref="A1:O325"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.8636363636364" style="16" customWidth="1"/>
-    <col min="2" max="2" width="14.1909090909091" style="9" customWidth="1"/>
-    <col min="3" max="3" width="12.2818181818182" style="9" customWidth="1"/>
+    <col min="1" max="1" width="43.8666666666667" style="16" customWidth="1"/>
+    <col min="2" max="2" width="14.1904761904762" style="9" customWidth="1"/>
+    <col min="3" max="3" width="12.2857142857143" style="9" customWidth="1"/>
     <col min="4" max="4" width="27" style="9" customWidth="1"/>
-    <col min="5" max="5" width="12.5727272727273" style="9" customWidth="1"/>
-    <col min="6" max="6" width="43.3909090909091" style="9" customWidth="1"/>
-    <col min="7" max="7" width="24.7818181818182" style="9" customWidth="1"/>
-    <col min="8" max="8" width="27.2636363636364" style="9" customWidth="1"/>
-    <col min="9" max="9" width="32.7454545454545" style="9" customWidth="1"/>
-    <col min="10" max="10" width="5.85454545454545" style="9" customWidth="1"/>
-    <col min="11" max="12" width="7.42727272727273" style="9" customWidth="1"/>
-    <col min="13" max="14" width="15.4272727272727" style="9" customWidth="1"/>
+    <col min="5" max="5" width="12.5714285714286" style="9" customWidth="1"/>
+    <col min="6" max="6" width="43.3904761904762" style="9" customWidth="1"/>
+    <col min="7" max="7" width="24.7809523809524" style="9" customWidth="1"/>
+    <col min="8" max="8" width="27.2666666666667" style="9" customWidth="1"/>
+    <col min="9" max="9" width="32.7428571428571" style="9" customWidth="1"/>
+    <col min="10" max="10" width="5.85714285714286" style="9" customWidth="1"/>
+    <col min="11" max="12" width="7.42857142857143" style="9" customWidth="1"/>
+    <col min="13" max="14" width="15.4285714285714" style="9" customWidth="1"/>
     <col min="15" max="15" width="9" style="13"/>
     <col min="16" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" customHeight="1" spans="1:14">
+    <row r="1" s="9" customFormat="1" customHeight="1" spans="1:15">
       <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
@@ -4168,15 +4189,15 @@
       <c r="L1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="18" t="s">
         <v>19</v>
       </c>
       <c r="N1" s="17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:9">
-      <c r="A2" s="18" t="s">
+    <row r="2" customHeight="1" spans="1:15">
+      <c r="A2" s="19" t="s">
         <v>92</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -4200,10 +4221,10 @@
       <c r="H2" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="22"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:9">
-      <c r="A3" s="18" t="s">
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:15">
+      <c r="A3" s="19" t="s">
         <v>97</v>
       </c>
       <c r="B3" s="9" t="s">
@@ -4227,10 +4248,10 @@
       <c r="H3" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="22"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:9">
-      <c r="A4" s="18" t="s">
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:15">
+      <c r="A4" s="19" t="s">
         <v>98</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -4254,10 +4275,10 @@
       <c r="H4" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I4" s="22"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:9">
-      <c r="A5" s="18" t="s">
+      <c r="I4" s="20"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:15">
+      <c r="A5" s="19" t="s">
         <v>99</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -4281,10 +4302,10 @@
       <c r="H5" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I5" s="22"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="18" t="s">
+      <c r="I5" s="20"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:15">
+      <c r="A6" s="19" t="s">
         <v>100</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -4308,10 +4329,10 @@
       <c r="H6" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="20"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>101</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -4335,7 +4356,7 @@
       <c r="H7" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I7" s="22"/>
+      <c r="I7" s="20"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
@@ -4344,7 +4365,7 @@
       <c r="O7" s="13"/>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>102</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -4368,7 +4389,7 @@
       <c r="H8" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I8" s="22"/>
+      <c r="I8" s="20"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
@@ -4377,7 +4398,7 @@
       <c r="O8" s="13"/>
     </row>
     <row r="9" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>103</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -4401,7 +4422,7 @@
       <c r="H9" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="20"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
@@ -4410,7 +4431,7 @@
       <c r="O9" s="13"/>
     </row>
     <row r="10" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>104</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -4434,7 +4455,7 @@
       <c r="H10" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I10" s="22"/>
+      <c r="I10" s="20"/>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
@@ -4443,7 +4464,7 @@
       <c r="O10" s="13"/>
     </row>
     <row r="11" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>105</v>
       </c>
       <c r="B11" s="9" t="s">
@@ -4458,14 +4479,16 @@
       <c r="E11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="9"/>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
       <c r="G11" s="9" t="s">
         <v>95</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I11" s="22"/>
+      <c r="I11" s="20"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -4474,7 +4497,7 @@
       <c r="O11" s="13"/>
     </row>
     <row r="12" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>106</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -4489,14 +4512,16 @@
       <c r="E12" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="9"/>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
       <c r="G12" s="9" t="s">
         <v>95</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="20"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
@@ -4505,7 +4530,7 @@
       <c r="O12" s="13"/>
     </row>
     <row r="13" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>107</v>
       </c>
       <c r="B13" s="9" t="s">
@@ -4520,14 +4545,16 @@
       <c r="E13" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="9"/>
+      <c r="F13" s="9">
+        <v>0</v>
+      </c>
       <c r="G13" s="9" t="s">
         <v>95</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="22"/>
+      <c r="I13" s="20"/>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
@@ -4535,8 +4562,8 @@
       <c r="N13" s="9"/>
       <c r="O13" s="13"/>
     </row>
-    <row r="14" customHeight="1" spans="1:9">
-      <c r="A14" s="18" t="s">
+    <row r="14" customHeight="1" spans="1:15">
+      <c r="A14" s="19" t="s">
         <v>108</v>
       </c>
       <c r="B14" s="9" t="s">
@@ -4560,12 +4587,12 @@
       <c r="H14" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="20" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:9">
-      <c r="A15" s="18" t="s">
+    <row r="15" customHeight="1" spans="1:15">
+      <c r="A15" s="19" t="s">
         <v>110</v>
       </c>
       <c r="B15" s="9" t="s">
@@ -4589,12 +4616,12 @@
       <c r="H15" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:9">
-      <c r="A16" s="18" t="s">
+    <row r="16" customHeight="1" spans="1:15">
+      <c r="A16" s="19" t="s">
         <v>112</v>
       </c>
       <c r="B16" s="9" t="s">
@@ -4618,7 +4645,7 @@
       <c r="H16" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="20" t="s">
         <v>113</v>
       </c>
     </row>
@@ -4631,7 +4658,7 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="22"/>
+      <c r="I17" s="20"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
@@ -4640,7 +4667,7 @@
       <c r="O17" s="13"/>
     </row>
     <row r="18" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="21" t="s">
         <v>114</v>
       </c>
       <c r="B18" s="9" t="s">
@@ -4664,7 +4691,7 @@
       <c r="H18" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I18" s="22"/>
+      <c r="I18" s="20"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
@@ -4672,8 +4699,8 @@
       <c r="N18" s="9"/>
       <c r="O18" s="13"/>
     </row>
-    <row r="19" customHeight="1" spans="1:9">
-      <c r="A19" s="19" t="s">
+    <row r="19" customHeight="1" spans="1:15">
+      <c r="A19" s="21" t="s">
         <v>115</v>
       </c>
       <c r="B19" s="9" t="s">
@@ -4701,8 +4728,8 @@
         <v>116</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:9">
-      <c r="A20" s="19" t="s">
+    <row r="20" customHeight="1" spans="1:15">
+      <c r="A20" s="21" t="s">
         <v>117</v>
       </c>
       <c r="B20" s="9" t="s">
@@ -4731,7 +4758,7 @@
       </c>
     </row>
     <row r="21" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="21" t="s">
         <v>119</v>
       </c>
       <c r="B21" s="9" t="s">
@@ -4755,7 +4782,7 @@
       <c r="H21" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I21" s="22"/>
+      <c r="I21" s="20"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
@@ -4764,7 +4791,7 @@
       <c r="O21" s="13"/>
     </row>
     <row r="22" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="21" t="s">
         <v>120</v>
       </c>
       <c r="B22" s="9" t="s">
@@ -4788,7 +4815,7 @@
       <c r="H22" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I22" s="22"/>
+      <c r="I22" s="20"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
@@ -4797,7 +4824,7 @@
       <c r="O22" s="13"/>
     </row>
     <row r="23" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="21" t="s">
         <v>121</v>
       </c>
       <c r="B23" s="9" t="s">
@@ -4821,7 +4848,7 @@
       <c r="H23" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I23" s="22"/>
+      <c r="I23" s="20"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
@@ -4838,7 +4865,7 @@
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="22"/>
+      <c r="I24" s="20"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
@@ -4847,7 +4874,7 @@
       <c r="O24" s="13"/>
     </row>
     <row r="25" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>122</v>
       </c>
       <c r="B25" s="9" t="s">
@@ -4871,7 +4898,7 @@
       <c r="H25" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I25" s="22"/>
+      <c r="I25" s="20"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
@@ -4880,7 +4907,7 @@
       <c r="O25" s="13"/>
     </row>
     <row r="26" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="22" t="s">
         <v>123</v>
       </c>
       <c r="B26" s="9" t="s">
@@ -4904,7 +4931,7 @@
       <c r="H26" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I26" s="22"/>
+      <c r="I26" s="20"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
@@ -4913,7 +4940,7 @@
       <c r="O26" s="13"/>
     </row>
     <row r="27" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="22" t="s">
         <v>124</v>
       </c>
       <c r="B27" s="9" t="s">
@@ -4937,7 +4964,7 @@
       <c r="H27" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I27" s="22"/>
+      <c r="I27" s="20"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
@@ -4946,7 +4973,7 @@
       <c r="O27" s="13"/>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="22" t="s">
         <v>125</v>
       </c>
       <c r="B28" s="9" t="s">
@@ -4970,7 +4997,7 @@
       <c r="H28" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I28" s="22"/>
+      <c r="I28" s="20"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
@@ -4979,7 +5006,7 @@
       <c r="O28" s="13"/>
     </row>
     <row r="29" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="22" t="s">
         <v>126</v>
       </c>
       <c r="B29" s="9" t="s">
@@ -5003,7 +5030,7 @@
       <c r="H29" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I29" s="22"/>
+      <c r="I29" s="20"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
@@ -5012,7 +5039,7 @@
       <c r="O29" s="13"/>
     </row>
     <row r="30" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="22" t="s">
         <v>127</v>
       </c>
       <c r="B30" s="9" t="s">
@@ -5036,7 +5063,7 @@
       <c r="H30" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I30" s="22"/>
+      <c r="I30" s="20"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
@@ -5045,7 +5072,7 @@
       <c r="O30" s="13"/>
     </row>
     <row r="31" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="22" t="s">
         <v>128</v>
       </c>
       <c r="B31" s="9" t="s">
@@ -5069,7 +5096,7 @@
       <c r="H31" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I31" s="22"/>
+      <c r="I31" s="20"/>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
@@ -5086,7 +5113,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="22"/>
+      <c r="I32" s="20"/>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
@@ -5095,7 +5122,7 @@
       <c r="O32" s="13"/>
     </row>
     <row r="33" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="19" t="s">
         <v>129</v>
       </c>
       <c r="B33" s="9" t="s">
@@ -5119,7 +5146,7 @@
       <c r="H33" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I33" s="22"/>
+      <c r="I33" s="20"/>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
@@ -5128,7 +5155,7 @@
       <c r="O33" s="13"/>
     </row>
     <row r="34" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="19" t="s">
         <v>130</v>
       </c>
       <c r="B34" s="9" t="s">
@@ -5152,7 +5179,7 @@
       <c r="H34" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I34" s="22"/>
+      <c r="I34" s="20"/>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
@@ -5161,7 +5188,7 @@
       <c r="O34" s="13"/>
     </row>
     <row r="35" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="19" t="s">
         <v>131</v>
       </c>
       <c r="B35" s="9" t="s">
@@ -5185,7 +5212,7 @@
       <c r="H35" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I35" s="22"/>
+      <c r="I35" s="20"/>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
       <c r="L35" s="9"/>
@@ -5194,7 +5221,7 @@
       <c r="O35" s="13"/>
     </row>
     <row r="36" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="19" t="s">
         <v>132</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -5218,7 +5245,7 @@
       <c r="H36" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I36" s="22"/>
+      <c r="I36" s="20"/>
       <c r="J36" s="9"/>
       <c r="K36" s="9"/>
       <c r="L36" s="9"/>
@@ -5227,7 +5254,7 @@
       <c r="O36" s="13"/>
     </row>
     <row r="37" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="19" t="s">
         <v>133</v>
       </c>
       <c r="B37" s="9" t="s">
@@ -5251,7 +5278,7 @@
       <c r="H37" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I37" s="22"/>
+      <c r="I37" s="20"/>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
       <c r="L37" s="9"/>
@@ -5260,7 +5287,7 @@
       <c r="O37" s="13"/>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="19" t="s">
         <v>134</v>
       </c>
       <c r="B38" s="9" t="s">
@@ -5284,7 +5311,7 @@
       <c r="H38" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I38" s="22"/>
+      <c r="I38" s="20"/>
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
       <c r="L38" s="9"/>
@@ -5293,7 +5320,7 @@
       <c r="O38" s="13"/>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="19" t="s">
         <v>135</v>
       </c>
       <c r="B39" s="9" t="s">
@@ -5317,7 +5344,7 @@
       <c r="H39" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I39" s="22"/>
+      <c r="I39" s="20"/>
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
       <c r="L39" s="9"/>
@@ -5334,7 +5361,7 @@
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
-      <c r="I40" s="22"/>
+      <c r="I40" s="20"/>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
@@ -5343,7 +5370,7 @@
       <c r="O40" s="13"/>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A41" s="19" t="s">
+      <c r="A41" s="21" t="s">
         <v>136</v>
       </c>
       <c r="B41" s="9" t="s">
@@ -5367,7 +5394,7 @@
       <c r="H41" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I41" s="22"/>
+      <c r="I41" s="20"/>
       <c r="J41" s="9"/>
       <c r="K41" s="9"/>
       <c r="L41" s="9"/>
@@ -5376,7 +5403,7 @@
       <c r="O41" s="13"/>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="21" t="s">
         <v>137</v>
       </c>
       <c r="B42" s="9" t="s">
@@ -5400,7 +5427,7 @@
       <c r="H42" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I42" s="22"/>
+      <c r="I42" s="20"/>
       <c r="J42" s="9"/>
       <c r="K42" s="9"/>
       <c r="L42" s="9"/>
@@ -5409,7 +5436,7 @@
       <c r="O42" s="13"/>
     </row>
     <row r="43" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A43" s="19" t="s">
+      <c r="A43" s="21" t="s">
         <v>138</v>
       </c>
       <c r="B43" s="9" t="s">
@@ -5433,7 +5460,7 @@
       <c r="H43" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I43" s="22"/>
+      <c r="I43" s="20"/>
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
@@ -5442,7 +5469,7 @@
       <c r="O43" s="13"/>
     </row>
     <row r="44" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="21" t="s">
         <v>139</v>
       </c>
       <c r="B44" s="9" t="s">
@@ -5466,7 +5493,7 @@
       <c r="H44" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I44" s="22"/>
+      <c r="I44" s="20"/>
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
       <c r="L44" s="9"/>
@@ -5475,7 +5502,7 @@
       <c r="O44" s="13"/>
     </row>
     <row r="45" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A45" s="19" t="s">
+      <c r="A45" s="21" t="s">
         <v>140</v>
       </c>
       <c r="B45" s="9" t="s">
@@ -5499,7 +5526,7 @@
       <c r="H45" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I45" s="22"/>
+      <c r="I45" s="20"/>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
@@ -5508,7 +5535,7 @@
       <c r="O45" s="13"/>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A46" s="19" t="s">
+      <c r="A46" s="21" t="s">
         <v>141</v>
       </c>
       <c r="B46" s="9" t="s">
@@ -5532,7 +5559,7 @@
       <c r="H46" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I46" s="22"/>
+      <c r="I46" s="20"/>
       <c r="J46" s="9"/>
       <c r="K46" s="9"/>
       <c r="L46" s="9"/>
@@ -5541,7 +5568,7 @@
       <c r="O46" s="13"/>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A47" s="19" t="s">
+      <c r="A47" s="21" t="s">
         <v>142</v>
       </c>
       <c r="B47" s="9" t="s">
@@ -5565,7 +5592,7 @@
       <c r="H47" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I47" s="22"/>
+      <c r="I47" s="20"/>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
       <c r="L47" s="9"/>
@@ -5582,7 +5609,7 @@
       <c r="F48" s="9"/>
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
-      <c r="I48" s="22"/>
+      <c r="I48" s="20"/>
       <c r="J48" s="9"/>
       <c r="K48" s="9"/>
       <c r="L48" s="9"/>
@@ -5591,7 +5618,7 @@
       <c r="O48" s="13"/>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A49" s="20" t="s">
+      <c r="A49" s="22" t="s">
         <v>143</v>
       </c>
       <c r="B49" s="9" t="s">
@@ -5615,7 +5642,7 @@
       <c r="H49" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I49" s="22"/>
+      <c r="I49" s="20"/>
       <c r="J49" s="9"/>
       <c r="K49" s="9"/>
       <c r="L49" s="9"/>
@@ -5624,7 +5651,7 @@
       <c r="O49" s="13"/>
     </row>
     <row r="50" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A50" s="20" t="s">
+      <c r="A50" s="22" t="s">
         <v>144</v>
       </c>
       <c r="B50" s="9" t="s">
@@ -5648,7 +5675,7 @@
       <c r="H50" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I50" s="22"/>
+      <c r="I50" s="20"/>
       <c r="J50" s="9"/>
       <c r="K50" s="9"/>
       <c r="L50" s="9"/>
@@ -5657,7 +5684,7 @@
       <c r="O50" s="13"/>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A51" s="20" t="s">
+      <c r="A51" s="22" t="s">
         <v>145</v>
       </c>
       <c r="B51" s="9" t="s">
@@ -5681,7 +5708,7 @@
       <c r="H51" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I51" s="22"/>
+      <c r="I51" s="20"/>
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
       <c r="L51" s="9"/>
@@ -5690,7 +5717,7 @@
       <c r="O51" s="13"/>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A52" s="20" t="s">
+      <c r="A52" s="22" t="s">
         <v>146</v>
       </c>
       <c r="B52" s="9" t="s">
@@ -5714,7 +5741,7 @@
       <c r="H52" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I52" s="22"/>
+      <c r="I52" s="20"/>
       <c r="J52" s="9"/>
       <c r="K52" s="9"/>
       <c r="L52" s="9"/>
@@ -5723,7 +5750,7 @@
       <c r="O52" s="13"/>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A53" s="20" t="s">
+      <c r="A53" s="22" t="s">
         <v>147</v>
       </c>
       <c r="B53" s="9" t="s">
@@ -5747,7 +5774,7 @@
       <c r="H53" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I53" s="22"/>
+      <c r="I53" s="20"/>
       <c r="J53" s="9"/>
       <c r="K53" s="9"/>
       <c r="L53" s="9"/>
@@ -5756,7 +5783,7 @@
       <c r="O53" s="13"/>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A54" s="20" t="s">
+      <c r="A54" s="22" t="s">
         <v>148</v>
       </c>
       <c r="B54" s="9" t="s">
@@ -5780,7 +5807,7 @@
       <c r="H54" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I54" s="22"/>
+      <c r="I54" s="20"/>
       <c r="J54" s="9"/>
       <c r="K54" s="9"/>
       <c r="L54" s="9"/>
@@ -5789,7 +5816,7 @@
       <c r="O54" s="13"/>
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A55" s="20" t="s">
+      <c r="A55" s="22" t="s">
         <v>149</v>
       </c>
       <c r="B55" s="9" t="s">
@@ -5813,7 +5840,7 @@
       <c r="H55" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I55" s="22"/>
+      <c r="I55" s="20"/>
       <c r="J55" s="9"/>
       <c r="K55" s="9"/>
       <c r="L55" s="9"/>
@@ -5830,7 +5857,7 @@
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
-      <c r="I56" s="22"/>
+      <c r="I56" s="20"/>
       <c r="J56" s="9"/>
       <c r="K56" s="9"/>
       <c r="L56" s="9"/>
@@ -5839,7 +5866,7 @@
       <c r="O56" s="13"/>
     </row>
     <row r="57" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A57" s="18" t="s">
+      <c r="A57" s="19" t="s">
         <v>150</v>
       </c>
       <c r="B57" s="9" t="s">
@@ -5863,7 +5890,7 @@
       <c r="H57" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I57" s="22"/>
+      <c r="I57" s="20"/>
       <c r="J57" s="9"/>
       <c r="K57" s="9"/>
       <c r="L57" s="9"/>
@@ -5872,7 +5899,7 @@
       <c r="O57" s="13"/>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="19" t="s">
         <v>151</v>
       </c>
       <c r="B58" s="9" t="s">
@@ -5907,7 +5934,7 @@
       <c r="O58" s="13"/>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A59" s="18" t="s">
+      <c r="A59" s="19" t="s">
         <v>152</v>
       </c>
       <c r="B59" s="9" t="s">
@@ -5942,7 +5969,7 @@
       <c r="O59" s="13"/>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="19" t="s">
         <v>153</v>
       </c>
       <c r="B60" s="9" t="s">
@@ -5966,7 +5993,7 @@
       <c r="H60" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I60" s="22"/>
+      <c r="I60" s="20"/>
       <c r="J60" s="9"/>
       <c r="K60" s="9"/>
       <c r="L60" s="9"/>
@@ -5975,7 +6002,7 @@
       <c r="O60" s="13"/>
     </row>
     <row r="61" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A61" s="18" t="s">
+      <c r="A61" s="19" t="s">
         <v>154</v>
       </c>
       <c r="B61" s="9" t="s">
@@ -5999,7 +6026,7 @@
       <c r="H61" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I61" s="22"/>
+      <c r="I61" s="20"/>
       <c r="J61" s="9"/>
       <c r="K61" s="9"/>
       <c r="L61" s="9"/>
@@ -6008,7 +6035,7 @@
       <c r="O61" s="13"/>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A62" s="18" t="s">
+      <c r="A62" s="19" t="s">
         <v>155</v>
       </c>
       <c r="B62" s="9" t="s">
@@ -6032,7 +6059,7 @@
       <c r="H62" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I62" s="22"/>
+      <c r="I62" s="20"/>
       <c r="J62" s="9"/>
       <c r="K62" s="9"/>
       <c r="L62" s="9"/>
@@ -6049,7 +6076,7 @@
       <c r="F63" s="9"/>
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
-      <c r="I63" s="22"/>
+      <c r="I63" s="20"/>
       <c r="J63" s="9"/>
       <c r="K63" s="9"/>
       <c r="L63" s="9"/>
@@ -6058,7 +6085,7 @@
       <c r="O63" s="13"/>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A64" s="19" t="s">
+      <c r="A64" s="21" t="s">
         <v>156</v>
       </c>
       <c r="B64" s="9" t="s">
@@ -6082,7 +6109,7 @@
       <c r="H64" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I64" s="22"/>
+      <c r="I64" s="20"/>
       <c r="J64" s="9"/>
       <c r="K64" s="9"/>
       <c r="L64" s="9"/>
@@ -6091,7 +6118,7 @@
       <c r="O64" s="13"/>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A65" s="19" t="s">
+      <c r="A65" s="21" t="s">
         <v>157</v>
       </c>
       <c r="B65" s="9" t="s">
@@ -6126,7 +6153,7 @@
       <c r="O65" s="13"/>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A66" s="19" t="s">
+      <c r="A66" s="21" t="s">
         <v>158</v>
       </c>
       <c r="B66" s="9" t="s">
@@ -6161,7 +6188,7 @@
       <c r="O66" s="13"/>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A67" s="19" t="s">
+      <c r="A67" s="21" t="s">
         <v>159</v>
       </c>
       <c r="B67" s="9" t="s">
@@ -6185,7 +6212,7 @@
       <c r="H67" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I67" s="22"/>
+      <c r="I67" s="20"/>
       <c r="J67" s="9"/>
       <c r="K67" s="9"/>
       <c r="L67" s="9"/>
@@ -6194,7 +6221,7 @@
       <c r="O67" s="13"/>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A68" s="19" t="s">
+      <c r="A68" s="21" t="s">
         <v>160</v>
       </c>
       <c r="B68" s="9" t="s">
@@ -6218,7 +6245,7 @@
       <c r="H68" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I68" s="22"/>
+      <c r="I68" s="20"/>
       <c r="J68" s="9"/>
       <c r="K68" s="9"/>
       <c r="L68" s="9"/>
@@ -6227,7 +6254,7 @@
       <c r="O68" s="13"/>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A69" s="19" t="s">
+      <c r="A69" s="21" t="s">
         <v>161</v>
       </c>
       <c r="B69" s="9" t="s">
@@ -6251,7 +6278,7 @@
       <c r="H69" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I69" s="22"/>
+      <c r="I69" s="20"/>
       <c r="J69" s="9"/>
       <c r="K69" s="9"/>
       <c r="L69" s="9"/>
@@ -6268,7 +6295,7 @@
       <c r="F70" s="9"/>
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
-      <c r="I70" s="22"/>
+      <c r="I70" s="20"/>
       <c r="J70" s="9"/>
       <c r="K70" s="9"/>
       <c r="L70" s="9"/>
@@ -6277,7 +6304,7 @@
       <c r="O70" s="13"/>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A71" s="20" t="s">
+      <c r="A71" s="22" t="s">
         <v>162</v>
       </c>
       <c r="B71" s="9" t="s">
@@ -6301,7 +6328,7 @@
       <c r="H71" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I71" s="22"/>
+      <c r="I71" s="20"/>
       <c r="J71" s="9"/>
       <c r="K71" s="9"/>
       <c r="L71" s="9"/>
@@ -6310,7 +6337,7 @@
       <c r="O71" s="13"/>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A72" s="20" t="s">
+      <c r="A72" s="22" t="s">
         <v>163</v>
       </c>
       <c r="B72" s="9" t="s">
@@ -6345,7 +6372,7 @@
       <c r="O72" s="13"/>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A73" s="20" t="s">
+      <c r="A73" s="22" t="s">
         <v>164</v>
       </c>
       <c r="B73" s="9" t="s">
@@ -6380,7 +6407,7 @@
       <c r="O73" s="13"/>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A74" s="20" t="s">
+      <c r="A74" s="22" t="s">
         <v>165</v>
       </c>
       <c r="B74" s="9" t="s">
@@ -6404,7 +6431,7 @@
       <c r="H74" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I74" s="22"/>
+      <c r="I74" s="20"/>
       <c r="J74" s="9"/>
       <c r="K74" s="9"/>
       <c r="L74" s="9"/>
@@ -6413,7 +6440,7 @@
       <c r="O74" s="13"/>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A75" s="20" t="s">
+      <c r="A75" s="22" t="s">
         <v>166</v>
       </c>
       <c r="B75" s="9" t="s">
@@ -6437,7 +6464,7 @@
       <c r="H75" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I75" s="22"/>
+      <c r="I75" s="20"/>
       <c r="J75" s="9"/>
       <c r="K75" s="9"/>
       <c r="L75" s="9"/>
@@ -6446,7 +6473,7 @@
       <c r="O75" s="13"/>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A76" s="20" t="s">
+      <c r="A76" s="22" t="s">
         <v>167</v>
       </c>
       <c r="B76" s="9" t="s">
@@ -6470,7 +6497,7 @@
       <c r="H76" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I76" s="22"/>
+      <c r="I76" s="20"/>
       <c r="J76" s="9"/>
       <c r="K76" s="9"/>
       <c r="L76" s="9"/>
@@ -6487,7 +6514,7 @@
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
-      <c r="I77" s="22"/>
+      <c r="I77" s="20"/>
       <c r="J77" s="9"/>
       <c r="K77" s="9"/>
       <c r="L77" s="9"/>
@@ -6495,8 +6522,8 @@
       <c r="N77" s="9"/>
       <c r="O77" s="13"/>
     </row>
-    <row r="78" customHeight="1" spans="1:9">
-      <c r="A78" s="18" t="s">
+    <row r="78" customHeight="1" spans="1:15">
+      <c r="A78" s="19" t="s">
         <v>168</v>
       </c>
       <c r="B78" s="9" t="s">
@@ -6520,10 +6547,10 @@
       <c r="H78" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I78" s="22"/>
+      <c r="I78" s="20"/>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A79" s="18" t="s">
+      <c r="A79" s="19" t="s">
         <v>169</v>
       </c>
       <c r="B79" s="9" t="s">
@@ -6547,7 +6574,7 @@
       <c r="H79" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I79" s="22"/>
+      <c r="I79" s="20"/>
       <c r="J79" s="9"/>
       <c r="K79" s="9"/>
       <c r="L79" s="9"/>
@@ -6556,7 +6583,7 @@
       <c r="O79" s="13"/>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A80" s="18" t="s">
+      <c r="A80" s="19" t="s">
         <v>168</v>
       </c>
       <c r="B80" s="9" t="s">
@@ -6591,7 +6618,7 @@
       <c r="O80" s="13"/>
     </row>
     <row r="81" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A81" s="18" t="s">
+      <c r="A81" s="19" t="s">
         <v>170</v>
       </c>
       <c r="B81" s="9" t="s">
@@ -6615,7 +6642,7 @@
       <c r="H81" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I81" s="22"/>
+      <c r="I81" s="20"/>
       <c r="J81" s="9"/>
       <c r="K81" s="9"/>
       <c r="L81" s="9"/>
@@ -6624,7 +6651,7 @@
       <c r="O81" s="13"/>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A82" s="18" t="s">
+      <c r="A82" s="19" t="s">
         <v>171</v>
       </c>
       <c r="B82" s="9" t="s">
@@ -6648,7 +6675,7 @@
       <c r="H82" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I82" s="22"/>
+      <c r="I82" s="20"/>
       <c r="J82" s="9"/>
       <c r="K82" s="9"/>
       <c r="L82" s="9"/>
@@ -6657,7 +6684,7 @@
       <c r="O82" s="13"/>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A83" s="18" t="s">
+      <c r="A83" s="19" t="s">
         <v>172</v>
       </c>
       <c r="B83" s="9" t="s">
@@ -6681,7 +6708,7 @@
       <c r="H83" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I83" s="22"/>
+      <c r="I83" s="20"/>
       <c r="J83" s="9"/>
       <c r="K83" s="9"/>
       <c r="L83" s="9"/>
@@ -6689,8 +6716,8 @@
       <c r="N83" s="9"/>
       <c r="O83" s="13"/>
     </row>
-    <row r="85" customHeight="1" spans="1:9">
-      <c r="A85" s="19" t="s">
+    <row r="85" customHeight="1" spans="1:15">
+      <c r="A85" s="21" t="s">
         <v>173</v>
       </c>
       <c r="B85" s="9" t="s">
@@ -6714,10 +6741,10 @@
       <c r="H85" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I85" s="22"/>
+      <c r="I85" s="20"/>
     </row>
     <row r="86" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A86" s="19" t="s">
+      <c r="A86" s="21" t="s">
         <v>174</v>
       </c>
       <c r="B86" s="9" t="s">
@@ -6741,7 +6768,7 @@
       <c r="H86" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I86" s="22"/>
+      <c r="I86" s="20"/>
       <c r="J86" s="9"/>
       <c r="K86" s="9"/>
       <c r="L86" s="9"/>
@@ -6750,7 +6777,7 @@
       <c r="O86" s="13"/>
     </row>
     <row r="87" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A87" s="19" t="s">
+      <c r="A87" s="21" t="s">
         <v>173</v>
       </c>
       <c r="B87" s="9" t="s">
@@ -6785,7 +6812,7 @@
       <c r="O87" s="13"/>
     </row>
     <row r="88" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A88" s="19" t="s">
+      <c r="A88" s="21" t="s">
         <v>175</v>
       </c>
       <c r="B88" s="9" t="s">
@@ -6809,7 +6836,7 @@
       <c r="H88" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I88" s="22"/>
+      <c r="I88" s="20"/>
       <c r="J88" s="9"/>
       <c r="K88" s="9"/>
       <c r="L88" s="9"/>
@@ -6818,7 +6845,7 @@
       <c r="O88" s="13"/>
     </row>
     <row r="89" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A89" s="19" t="s">
+      <c r="A89" s="21" t="s">
         <v>176</v>
       </c>
       <c r="B89" s="9" t="s">
@@ -6842,7 +6869,7 @@
       <c r="H89" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I89" s="22"/>
+      <c r="I89" s="20"/>
       <c r="J89" s="9"/>
       <c r="K89" s="9"/>
       <c r="L89" s="9"/>
@@ -6851,7 +6878,7 @@
       <c r="O89" s="13"/>
     </row>
     <row r="90" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A90" s="19" t="s">
+      <c r="A90" s="21" t="s">
         <v>177</v>
       </c>
       <c r="B90" s="9" t="s">
@@ -6875,7 +6902,7 @@
       <c r="H90" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I90" s="22"/>
+      <c r="I90" s="20"/>
       <c r="J90" s="9"/>
       <c r="K90" s="9"/>
       <c r="L90" s="9"/>
@@ -6901,7 +6928,7 @@
       <c r="O91" s="26"/>
     </row>
     <row r="92" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A92" s="20" t="s">
+      <c r="A92" s="22" t="s">
         <v>178</v>
       </c>
       <c r="B92" s="9" t="s">
@@ -6925,7 +6952,7 @@
       <c r="H92" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I92" s="22"/>
+      <c r="I92" s="20"/>
       <c r="J92" s="9"/>
       <c r="K92" s="9"/>
       <c r="L92" s="9"/>
@@ -6934,7 +6961,7 @@
       <c r="O92" s="13"/>
     </row>
     <row r="93" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A93" s="20" t="s">
+      <c r="A93" s="22" t="s">
         <v>179</v>
       </c>
       <c r="B93" s="9" t="s">
@@ -6958,7 +6985,7 @@
       <c r="H93" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I93" s="22"/>
+      <c r="I93" s="20"/>
       <c r="J93" s="9"/>
       <c r="K93" s="9"/>
       <c r="L93" s="9"/>
@@ -6967,7 +6994,7 @@
       <c r="O93" s="13"/>
     </row>
     <row r="94" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A94" s="20" t="s">
+      <c r="A94" s="22" t="s">
         <v>178</v>
       </c>
       <c r="B94" s="9" t="s">
@@ -7002,7 +7029,7 @@
       <c r="O94" s="13"/>
     </row>
     <row r="95" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A95" s="20" t="s">
+      <c r="A95" s="22" t="s">
         <v>180</v>
       </c>
       <c r="B95" s="9" t="s">
@@ -7026,7 +7053,7 @@
       <c r="H95" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I95" s="22"/>
+      <c r="I95" s="20"/>
       <c r="J95" s="9"/>
       <c r="K95" s="9"/>
       <c r="L95" s="9"/>
@@ -7035,7 +7062,7 @@
       <c r="O95" s="13"/>
     </row>
     <row r="96" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A96" s="20" t="s">
+      <c r="A96" s="22" t="s">
         <v>181</v>
       </c>
       <c r="B96" s="9" t="s">
@@ -7059,7 +7086,7 @@
       <c r="H96" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I96" s="22"/>
+      <c r="I96" s="20"/>
       <c r="J96" s="9"/>
       <c r="K96" s="9"/>
       <c r="L96" s="9"/>
@@ -7068,7 +7095,7 @@
       <c r="O96" s="13"/>
     </row>
     <row r="97" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A97" s="20" t="s">
+      <c r="A97" s="22" t="s">
         <v>182</v>
       </c>
       <c r="B97" s="9" t="s">
@@ -7092,7 +7119,7 @@
       <c r="H97" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I97" s="22"/>
+      <c r="I97" s="20"/>
       <c r="J97" s="9"/>
       <c r="K97" s="9"/>
       <c r="L97" s="9"/>
@@ -7118,7 +7145,7 @@
       <c r="O98" s="13"/>
     </row>
     <row r="99" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A99" s="18" t="s">
+      <c r="A99" s="19" t="s">
         <v>183</v>
       </c>
       <c r="B99" s="9" t="s">
@@ -7142,7 +7169,7 @@
       <c r="H99" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I99" s="22"/>
+      <c r="I99" s="20"/>
       <c r="J99" s="9"/>
       <c r="K99" s="9"/>
       <c r="L99" s="9"/>
@@ -7151,7 +7178,7 @@
       <c r="O99" s="13"/>
     </row>
     <row r="100" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A100" s="18" t="s">
+      <c r="A100" s="19" t="s">
         <v>184</v>
       </c>
       <c r="B100" s="9" t="s">
@@ -7175,7 +7202,7 @@
       <c r="H100" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I100" s="22"/>
+      <c r="I100" s="20"/>
       <c r="J100" s="9"/>
       <c r="K100" s="9"/>
       <c r="L100" s="9"/>
@@ -7184,7 +7211,7 @@
       <c r="O100" s="13"/>
     </row>
     <row r="101" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A101" s="18" t="s">
+      <c r="A101" s="19" t="s">
         <v>183</v>
       </c>
       <c r="B101" s="9" t="s">
@@ -7219,7 +7246,7 @@
       <c r="O101" s="13"/>
     </row>
     <row r="102" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A102" s="18" t="s">
+      <c r="A102" s="19" t="s">
         <v>185</v>
       </c>
       <c r="B102" s="9" t="s">
@@ -7243,7 +7270,7 @@
       <c r="H102" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I102" s="22"/>
+      <c r="I102" s="20"/>
       <c r="J102" s="9"/>
       <c r="K102" s="9"/>
       <c r="L102" s="9"/>
@@ -7252,7 +7279,7 @@
       <c r="O102" s="13"/>
     </row>
     <row r="103" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A103" s="18" t="s">
+      <c r="A103" s="19" t="s">
         <v>186</v>
       </c>
       <c r="B103" s="9" t="s">
@@ -7276,7 +7303,7 @@
       <c r="H103" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I103" s="22"/>
+      <c r="I103" s="20"/>
       <c r="J103" s="9"/>
       <c r="K103" s="9"/>
       <c r="L103" s="9"/>
@@ -7285,7 +7312,7 @@
       <c r="O103" s="13"/>
     </row>
     <row r="104" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A104" s="18" t="s">
+      <c r="A104" s="19" t="s">
         <v>187</v>
       </c>
       <c r="B104" s="9" t="s">
@@ -7309,7 +7336,7 @@
       <c r="H104" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I104" s="22"/>
+      <c r="I104" s="20"/>
       <c r="J104" s="9"/>
       <c r="K104" s="9"/>
       <c r="L104" s="9"/>
@@ -7335,7 +7362,7 @@
       <c r="O105" s="26"/>
     </row>
     <row r="106" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A106" s="19" t="s">
+      <c r="A106" s="21" t="s">
         <v>188</v>
       </c>
       <c r="B106" s="9" t="s">
@@ -7359,7 +7386,7 @@
       <c r="H106" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I106" s="22"/>
+      <c r="I106" s="20"/>
       <c r="J106" s="9"/>
       <c r="K106" s="9"/>
       <c r="L106" s="9"/>
@@ -7368,7 +7395,7 @@
       <c r="O106" s="13"/>
     </row>
     <row r="107" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A107" s="19" t="s">
+      <c r="A107" s="21" t="s">
         <v>189</v>
       </c>
       <c r="B107" s="9" t="s">
@@ -7392,7 +7419,7 @@
       <c r="H107" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I107" s="22"/>
+      <c r="I107" s="20"/>
       <c r="J107" s="9"/>
       <c r="K107" s="9"/>
       <c r="L107" s="9"/>
@@ -7401,7 +7428,7 @@
       <c r="O107" s="13"/>
     </row>
     <row r="108" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A108" s="19" t="s">
+      <c r="A108" s="21" t="s">
         <v>188</v>
       </c>
       <c r="B108" s="9" t="s">
@@ -7436,7 +7463,7 @@
       <c r="O108" s="13"/>
     </row>
     <row r="109" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A109" s="19" t="s">
+      <c r="A109" s="21" t="s">
         <v>190</v>
       </c>
       <c r="B109" s="9" t="s">
@@ -7460,7 +7487,7 @@
       <c r="H109" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I109" s="22"/>
+      <c r="I109" s="20"/>
       <c r="J109" s="9"/>
       <c r="K109" s="9"/>
       <c r="L109" s="9"/>
@@ -7469,7 +7496,7 @@
       <c r="O109" s="13"/>
     </row>
     <row r="110" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A110" s="19" t="s">
+      <c r="A110" s="21" t="s">
         <v>191</v>
       </c>
       <c r="B110" s="9" t="s">
@@ -7493,7 +7520,7 @@
       <c r="H110" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I110" s="22"/>
+      <c r="I110" s="20"/>
       <c r="J110" s="9"/>
       <c r="K110" s="9"/>
       <c r="L110" s="9"/>
@@ -7502,7 +7529,7 @@
       <c r="O110" s="13"/>
     </row>
     <row r="111" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A111" s="19" t="s">
+      <c r="A111" s="21" t="s">
         <v>192</v>
       </c>
       <c r="B111" s="9" t="s">
@@ -7526,7 +7553,7 @@
       <c r="H111" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I111" s="22"/>
+      <c r="I111" s="20"/>
       <c r="J111" s="9"/>
       <c r="K111" s="9"/>
       <c r="L111" s="9"/>
@@ -7552,7 +7579,7 @@
       <c r="O112" s="26"/>
     </row>
     <row r="113" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A113" s="20" t="s">
+      <c r="A113" s="22" t="s">
         <v>193</v>
       </c>
       <c r="B113" s="9" t="s">
@@ -7576,7 +7603,7 @@
       <c r="H113" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I113" s="22"/>
+      <c r="I113" s="20"/>
       <c r="J113" s="9"/>
       <c r="K113" s="9"/>
       <c r="L113" s="9"/>
@@ -7585,7 +7612,7 @@
       <c r="O113" s="13"/>
     </row>
     <row r="114" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A114" s="20" t="s">
+      <c r="A114" s="22" t="s">
         <v>194</v>
       </c>
       <c r="B114" s="9" t="s">
@@ -7609,7 +7636,7 @@
       <c r="H114" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I114" s="22"/>
+      <c r="I114" s="20"/>
       <c r="J114" s="9"/>
       <c r="K114" s="9"/>
       <c r="L114" s="9"/>
@@ -7618,7 +7645,7 @@
       <c r="O114" s="13"/>
     </row>
     <row r="115" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A115" s="20" t="s">
+      <c r="A115" s="22" t="s">
         <v>193</v>
       </c>
       <c r="B115" s="9" t="s">
@@ -7653,7 +7680,7 @@
       <c r="O115" s="13"/>
     </row>
     <row r="116" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A116" s="20" t="s">
+      <c r="A116" s="22" t="s">
         <v>195</v>
       </c>
       <c r="B116" s="9" t="s">
@@ -7677,7 +7704,7 @@
       <c r="H116" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I116" s="22"/>
+      <c r="I116" s="20"/>
       <c r="J116" s="9"/>
       <c r="K116" s="9"/>
       <c r="L116" s="9"/>
@@ -7686,7 +7713,7 @@
       <c r="O116" s="13"/>
     </row>
     <row r="117" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A117" s="20" t="s">
+      <c r="A117" s="22" t="s">
         <v>196</v>
       </c>
       <c r="B117" s="9" t="s">
@@ -7710,7 +7737,7 @@
       <c r="H117" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I117" s="22"/>
+      <c r="I117" s="20"/>
       <c r="J117" s="9"/>
       <c r="K117" s="9"/>
       <c r="L117" s="9"/>
@@ -7719,7 +7746,7 @@
       <c r="O117" s="13"/>
     </row>
     <row r="118" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A118" s="20" t="s">
+      <c r="A118" s="22" t="s">
         <v>197</v>
       </c>
       <c r="B118" s="9" t="s">
@@ -7743,7 +7770,7 @@
       <c r="H118" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I118" s="22"/>
+      <c r="I118" s="20"/>
       <c r="J118" s="9"/>
       <c r="K118" s="9"/>
       <c r="L118" s="9"/>
@@ -7760,7 +7787,7 @@
       <c r="F119" s="9"/>
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
-      <c r="I119" s="22"/>
+      <c r="I119" s="20"/>
       <c r="J119" s="9"/>
       <c r="K119" s="9"/>
       <c r="L119" s="9"/>
@@ -7769,7 +7796,7 @@
       <c r="O119" s="13"/>
     </row>
     <row r="120" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A120" s="18" t="s">
+      <c r="A120" s="19" t="s">
         <v>198</v>
       </c>
       <c r="B120" s="9" t="s">
@@ -7793,7 +7820,7 @@
       <c r="H120" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I120" s="22"/>
+      <c r="I120" s="20"/>
       <c r="J120" s="9"/>
       <c r="K120" s="9"/>
       <c r="L120" s="9"/>
@@ -7802,7 +7829,7 @@
       <c r="O120" s="13"/>
     </row>
     <row r="121" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A121" s="18" t="s">
+      <c r="A121" s="19" t="s">
         <v>199</v>
       </c>
       <c r="B121" s="9" t="s">
@@ -7826,7 +7853,7 @@
       <c r="H121" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I121" s="22"/>
+      <c r="I121" s="20"/>
       <c r="J121" s="9"/>
       <c r="K121" s="9"/>
       <c r="L121" s="9"/>
@@ -7835,7 +7862,7 @@
       <c r="O121" s="13"/>
     </row>
     <row r="122" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A122" s="18" t="s">
+      <c r="A122" s="19" t="s">
         <v>198</v>
       </c>
       <c r="B122" s="9" t="s">
@@ -7870,7 +7897,7 @@
       <c r="O122" s="13"/>
     </row>
     <row r="123" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A123" s="18" t="s">
+      <c r="A123" s="19" t="s">
         <v>200</v>
       </c>
       <c r="B123" s="9" t="s">
@@ -7894,7 +7921,7 @@
       <c r="H123" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I123" s="22"/>
+      <c r="I123" s="20"/>
       <c r="J123" s="9"/>
       <c r="K123" s="9"/>
       <c r="L123" s="9"/>
@@ -7903,7 +7930,7 @@
       <c r="O123" s="13"/>
     </row>
     <row r="124" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A124" s="18" t="s">
+      <c r="A124" s="19" t="s">
         <v>201</v>
       </c>
       <c r="B124" s="9" t="s">
@@ -7927,7 +7954,7 @@
       <c r="H124" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I124" s="22"/>
+      <c r="I124" s="20"/>
       <c r="J124" s="9"/>
       <c r="K124" s="9"/>
       <c r="L124" s="9"/>
@@ -7936,7 +7963,7 @@
       <c r="O124" s="13"/>
     </row>
     <row r="125" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A125" s="18" t="s">
+      <c r="A125" s="19" t="s">
         <v>202</v>
       </c>
       <c r="B125" s="9" t="s">
@@ -7960,7 +7987,7 @@
       <c r="H125" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I125" s="22"/>
+      <c r="I125" s="20"/>
       <c r="J125" s="9"/>
       <c r="K125" s="9"/>
       <c r="L125" s="9"/>
@@ -7986,7 +8013,7 @@
       <c r="O126" s="26"/>
     </row>
     <row r="127" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A127" s="19" t="s">
+      <c r="A127" s="21" t="s">
         <v>203</v>
       </c>
       <c r="B127" s="9" t="s">
@@ -8010,7 +8037,7 @@
       <c r="H127" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I127" s="22"/>
+      <c r="I127" s="20"/>
       <c r="J127" s="9"/>
       <c r="K127" s="9"/>
       <c r="L127" s="9"/>
@@ -8019,7 +8046,7 @@
       <c r="O127" s="13"/>
     </row>
     <row r="128" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A128" s="19" t="s">
+      <c r="A128" s="21" t="s">
         <v>204</v>
       </c>
       <c r="B128" s="9" t="s">
@@ -8043,7 +8070,7 @@
       <c r="H128" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I128" s="22"/>
+      <c r="I128" s="20"/>
       <c r="J128" s="9"/>
       <c r="K128" s="9"/>
       <c r="L128" s="9"/>
@@ -8052,7 +8079,7 @@
       <c r="O128" s="13"/>
     </row>
     <row r="129" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A129" s="19" t="s">
+      <c r="A129" s="21" t="s">
         <v>203</v>
       </c>
       <c r="B129" s="9" t="s">
@@ -8087,7 +8114,7 @@
       <c r="O129" s="13"/>
     </row>
     <row r="130" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A130" s="19" t="s">
+      <c r="A130" s="21" t="s">
         <v>205</v>
       </c>
       <c r="B130" s="9" t="s">
@@ -8111,7 +8138,7 @@
       <c r="H130" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I130" s="22"/>
+      <c r="I130" s="20"/>
       <c r="J130" s="9"/>
       <c r="K130" s="9"/>
       <c r="L130" s="9"/>
@@ -8120,7 +8147,7 @@
       <c r="O130" s="13"/>
     </row>
     <row r="131" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A131" s="19" t="s">
+      <c r="A131" s="21" t="s">
         <v>206</v>
       </c>
       <c r="B131" s="9" t="s">
@@ -8144,7 +8171,7 @@
       <c r="H131" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I131" s="22"/>
+      <c r="I131" s="20"/>
       <c r="J131" s="9"/>
       <c r="K131" s="9"/>
       <c r="L131" s="9"/>
@@ -8153,7 +8180,7 @@
       <c r="O131" s="13"/>
     </row>
     <row r="132" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A132" s="19" t="s">
+      <c r="A132" s="21" t="s">
         <v>207</v>
       </c>
       <c r="B132" s="9" t="s">
@@ -8177,7 +8204,7 @@
       <c r="H132" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I132" s="22"/>
+      <c r="I132" s="20"/>
       <c r="J132" s="9"/>
       <c r="K132" s="9"/>
       <c r="L132" s="9"/>
@@ -8203,7 +8230,7 @@
       <c r="O133" s="26"/>
     </row>
     <row r="134" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A134" s="20" t="s">
+      <c r="A134" s="22" t="s">
         <v>208</v>
       </c>
       <c r="B134" s="9" t="s">
@@ -8227,7 +8254,7 @@
       <c r="H134" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I134" s="22"/>
+      <c r="I134" s="20"/>
       <c r="J134" s="9"/>
       <c r="K134" s="9"/>
       <c r="L134" s="9"/>
@@ -8236,7 +8263,7 @@
       <c r="O134" s="13"/>
     </row>
     <row r="135" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A135" s="20" t="s">
+      <c r="A135" s="22" t="s">
         <v>209</v>
       </c>
       <c r="B135" s="9" t="s">
@@ -8260,7 +8287,7 @@
       <c r="H135" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I135" s="22"/>
+      <c r="I135" s="20"/>
       <c r="J135" s="9"/>
       <c r="K135" s="9"/>
       <c r="L135" s="9"/>
@@ -8269,7 +8296,7 @@
       <c r="O135" s="13"/>
     </row>
     <row r="136" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A136" s="20" t="s">
+      <c r="A136" s="22" t="s">
         <v>208</v>
       </c>
       <c r="B136" s="9" t="s">
@@ -8304,7 +8331,7 @@
       <c r="O136" s="13"/>
     </row>
     <row r="137" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A137" s="20" t="s">
+      <c r="A137" s="22" t="s">
         <v>210</v>
       </c>
       <c r="B137" s="9" t="s">
@@ -8328,7 +8355,7 @@
       <c r="H137" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I137" s="22"/>
+      <c r="I137" s="20"/>
       <c r="J137" s="9"/>
       <c r="K137" s="9"/>
       <c r="L137" s="9"/>
@@ -8337,7 +8364,7 @@
       <c r="O137" s="13"/>
     </row>
     <row r="138" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A138" s="20" t="s">
+      <c r="A138" s="22" t="s">
         <v>211</v>
       </c>
       <c r="B138" s="9" t="s">
@@ -8361,7 +8388,7 @@
       <c r="H138" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I138" s="22"/>
+      <c r="I138" s="20"/>
       <c r="J138" s="9"/>
       <c r="K138" s="9"/>
       <c r="L138" s="9"/>
@@ -8370,7 +8397,7 @@
       <c r="O138" s="13"/>
     </row>
     <row r="139" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A139" s="20" t="s">
+      <c r="A139" s="22" t="s">
         <v>212</v>
       </c>
       <c r="B139" s="9" t="s">
@@ -8394,7 +8421,7 @@
       <c r="H139" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I139" s="22"/>
+      <c r="I139" s="20"/>
       <c r="J139" s="9"/>
       <c r="K139" s="9"/>
       <c r="L139" s="9"/>
@@ -8420,7 +8447,7 @@
       <c r="O140" s="26"/>
     </row>
     <row r="141" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A141" s="18" t="s">
+      <c r="A141" s="19" t="s">
         <v>213</v>
       </c>
       <c r="B141" s="9" t="s">
@@ -8444,7 +8471,7 @@
       <c r="H141" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I141" s="22"/>
+      <c r="I141" s="20"/>
       <c r="J141" s="9"/>
       <c r="K141" s="9"/>
       <c r="L141" s="9"/>
@@ -8453,7 +8480,7 @@
       <c r="O141" s="13"/>
     </row>
     <row r="142" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A142" s="18" t="s">
+      <c r="A142" s="19" t="s">
         <v>214</v>
       </c>
       <c r="B142" s="9" t="s">
@@ -8477,7 +8504,7 @@
       <c r="H142" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I142" s="22"/>
+      <c r="I142" s="20"/>
       <c r="J142" s="9"/>
       <c r="K142" s="9"/>
       <c r="L142" s="9"/>
@@ -8486,7 +8513,7 @@
       <c r="O142" s="13"/>
     </row>
     <row r="143" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A143" s="18" t="s">
+      <c r="A143" s="19" t="s">
         <v>213</v>
       </c>
       <c r="B143" s="9" t="s">
@@ -8521,7 +8548,7 @@
       <c r="O143" s="13"/>
     </row>
     <row r="144" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A144" s="18" t="s">
+      <c r="A144" s="19" t="s">
         <v>215</v>
       </c>
       <c r="B144" s="9" t="s">
@@ -8545,7 +8572,7 @@
       <c r="H144" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I144" s="22"/>
+      <c r="I144" s="20"/>
       <c r="J144" s="9"/>
       <c r="K144" s="9"/>
       <c r="L144" s="9"/>
@@ -8554,7 +8581,7 @@
       <c r="O144" s="13"/>
     </row>
     <row r="145" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A145" s="18" t="s">
+      <c r="A145" s="19" t="s">
         <v>216</v>
       </c>
       <c r="B145" s="9" t="s">
@@ -8578,7 +8605,7 @@
       <c r="H145" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I145" s="22"/>
+      <c r="I145" s="20"/>
       <c r="J145" s="9"/>
       <c r="K145" s="9"/>
       <c r="L145" s="9"/>
@@ -8587,7 +8614,7 @@
       <c r="O145" s="13"/>
     </row>
     <row r="146" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A146" s="18" t="s">
+      <c r="A146" s="19" t="s">
         <v>217</v>
       </c>
       <c r="B146" s="9" t="s">
@@ -8611,7 +8638,7 @@
       <c r="H146" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I146" s="22"/>
+      <c r="I146" s="20"/>
       <c r="J146" s="9"/>
       <c r="K146" s="9"/>
       <c r="L146" s="9"/>
@@ -8637,7 +8664,7 @@
       <c r="O147" s="26"/>
     </row>
     <row r="148" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A148" s="19" t="s">
+      <c r="A148" s="21" t="s">
         <v>218</v>
       </c>
       <c r="B148" s="9" t="s">
@@ -8661,7 +8688,7 @@
       <c r="H148" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I148" s="22"/>
+      <c r="I148" s="20"/>
       <c r="J148" s="9"/>
       <c r="K148" s="9"/>
       <c r="L148" s="9"/>
@@ -8670,7 +8697,7 @@
       <c r="O148" s="13"/>
     </row>
     <row r="149" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A149" s="19" t="s">
+      <c r="A149" s="21" t="s">
         <v>219</v>
       </c>
       <c r="B149" s="9" t="s">
@@ -8694,7 +8721,7 @@
       <c r="H149" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I149" s="22"/>
+      <c r="I149" s="20"/>
       <c r="J149" s="9"/>
       <c r="K149" s="9"/>
       <c r="L149" s="9"/>
@@ -8703,7 +8730,7 @@
       <c r="O149" s="13"/>
     </row>
     <row r="150" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A150" s="19" t="s">
+      <c r="A150" s="21" t="s">
         <v>218</v>
       </c>
       <c r="B150" s="9" t="s">
@@ -8738,7 +8765,7 @@
       <c r="O150" s="13"/>
     </row>
     <row r="151" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A151" s="19" t="s">
+      <c r="A151" s="21" t="s">
         <v>220</v>
       </c>
       <c r="B151" s="9" t="s">
@@ -8762,7 +8789,7 @@
       <c r="H151" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I151" s="22"/>
+      <c r="I151" s="20"/>
       <c r="J151" s="9"/>
       <c r="K151" s="9"/>
       <c r="L151" s="9"/>
@@ -8771,7 +8798,7 @@
       <c r="O151" s="13"/>
     </row>
     <row r="152" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A152" s="19" t="s">
+      <c r="A152" s="21" t="s">
         <v>221</v>
       </c>
       <c r="B152" s="9" t="s">
@@ -8795,7 +8822,7 @@
       <c r="H152" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I152" s="22"/>
+      <c r="I152" s="20"/>
       <c r="J152" s="9"/>
       <c r="K152" s="9"/>
       <c r="L152" s="9"/>
@@ -8804,7 +8831,7 @@
       <c r="O152" s="13"/>
     </row>
     <row r="153" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A153" s="19" t="s">
+      <c r="A153" s="21" t="s">
         <v>222</v>
       </c>
       <c r="B153" s="9" t="s">
@@ -8828,7 +8855,7 @@
       <c r="H153" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I153" s="22"/>
+      <c r="I153" s="20"/>
       <c r="J153" s="9"/>
       <c r="K153" s="9"/>
       <c r="L153" s="9"/>
@@ -8854,7 +8881,7 @@
       <c r="O154" s="26"/>
     </row>
     <row r="155" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A155" s="20" t="s">
+      <c r="A155" s="22" t="s">
         <v>223</v>
       </c>
       <c r="B155" s="9" t="s">
@@ -8878,7 +8905,7 @@
       <c r="H155" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I155" s="22"/>
+      <c r="I155" s="20"/>
       <c r="J155" s="9"/>
       <c r="K155" s="9"/>
       <c r="L155" s="9"/>
@@ -8887,7 +8914,7 @@
       <c r="O155" s="13"/>
     </row>
     <row r="156" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A156" s="20" t="s">
+      <c r="A156" s="22" t="s">
         <v>224</v>
       </c>
       <c r="B156" s="9" t="s">
@@ -8911,7 +8938,7 @@
       <c r="H156" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I156" s="22"/>
+      <c r="I156" s="20"/>
       <c r="J156" s="9"/>
       <c r="K156" s="9"/>
       <c r="L156" s="9"/>
@@ -8920,7 +8947,7 @@
       <c r="O156" s="13"/>
     </row>
     <row r="157" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A157" s="20" t="s">
+      <c r="A157" s="22" t="s">
         <v>223</v>
       </c>
       <c r="B157" s="9" t="s">
@@ -8955,7 +8982,7 @@
       <c r="O157" s="13"/>
     </row>
     <row r="158" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A158" s="20" t="s">
+      <c r="A158" s="22" t="s">
         <v>225</v>
       </c>
       <c r="B158" s="9" t="s">
@@ -8979,7 +9006,7 @@
       <c r="H158" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I158" s="22"/>
+      <c r="I158" s="20"/>
       <c r="J158" s="9"/>
       <c r="K158" s="9"/>
       <c r="L158" s="9"/>
@@ -8988,7 +9015,7 @@
       <c r="O158" s="13"/>
     </row>
     <row r="159" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A159" s="20" t="s">
+      <c r="A159" s="22" t="s">
         <v>226</v>
       </c>
       <c r="B159" s="9" t="s">
@@ -9012,7 +9039,7 @@
       <c r="H159" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I159" s="22"/>
+      <c r="I159" s="20"/>
       <c r="J159" s="9"/>
       <c r="K159" s="9"/>
       <c r="L159" s="9"/>
@@ -9021,7 +9048,7 @@
       <c r="O159" s="13"/>
     </row>
     <row r="160" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A160" s="20" t="s">
+      <c r="A160" s="22" t="s">
         <v>227</v>
       </c>
       <c r="B160" s="9" t="s">
@@ -9045,7 +9072,7 @@
       <c r="H160" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I160" s="22"/>
+      <c r="I160" s="20"/>
       <c r="J160" s="9"/>
       <c r="K160" s="9"/>
       <c r="L160" s="9"/>
@@ -9071,7 +9098,7 @@
       <c r="O161" s="26"/>
     </row>
     <row r="162" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A162" s="18" t="s">
+      <c r="A162" s="19" t="s">
         <v>228</v>
       </c>
       <c r="B162" s="9" t="s">
@@ -9095,7 +9122,7 @@
       <c r="H162" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I162" s="22"/>
+      <c r="I162" s="20"/>
       <c r="J162" s="9"/>
       <c r="K162" s="9"/>
       <c r="L162" s="9"/>
@@ -9104,7 +9131,7 @@
       <c r="O162" s="13"/>
     </row>
     <row r="163" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A163" s="18" t="s">
+      <c r="A163" s="19" t="s">
         <v>229</v>
       </c>
       <c r="B163" s="9" t="s">
@@ -9128,7 +9155,7 @@
       <c r="H163" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I163" s="22"/>
+      <c r="I163" s="20"/>
       <c r="J163" s="9"/>
       <c r="K163" s="9"/>
       <c r="L163" s="9"/>
@@ -9137,7 +9164,7 @@
       <c r="O163" s="13"/>
     </row>
     <row r="164" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A164" s="18" t="s">
+      <c r="A164" s="19" t="s">
         <v>228</v>
       </c>
       <c r="B164" s="9" t="s">
@@ -9172,7 +9199,7 @@
       <c r="O164" s="13"/>
     </row>
     <row r="165" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A165" s="18" t="s">
+      <c r="A165" s="19" t="s">
         <v>230</v>
       </c>
       <c r="B165" s="9" t="s">
@@ -9196,7 +9223,7 @@
       <c r="H165" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I165" s="22"/>
+      <c r="I165" s="20"/>
       <c r="J165" s="9"/>
       <c r="K165" s="9"/>
       <c r="L165" s="9"/>
@@ -9205,7 +9232,7 @@
       <c r="O165" s="13"/>
     </row>
     <row r="166" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A166" s="18" t="s">
+      <c r="A166" s="19" t="s">
         <v>231</v>
       </c>
       <c r="B166" s="9" t="s">
@@ -9229,7 +9256,7 @@
       <c r="H166" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I166" s="22"/>
+      <c r="I166" s="20"/>
       <c r="J166" s="9"/>
       <c r="K166" s="9"/>
       <c r="L166" s="9"/>
@@ -9238,7 +9265,7 @@
       <c r="O166" s="13"/>
     </row>
     <row r="167" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A167" s="18" t="s">
+      <c r="A167" s="19" t="s">
         <v>232</v>
       </c>
       <c r="B167" s="9" t="s">
@@ -9262,7 +9289,7 @@
       <c r="H167" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I167" s="22"/>
+      <c r="I167" s="20"/>
       <c r="J167" s="9"/>
       <c r="K167" s="9"/>
       <c r="L167" s="9"/>
@@ -9288,7 +9315,7 @@
       <c r="O168" s="26"/>
     </row>
     <row r="169" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A169" s="19" t="s">
+      <c r="A169" s="21" t="s">
         <v>233</v>
       </c>
       <c r="B169" s="9" t="s">
@@ -9312,7 +9339,7 @@
       <c r="H169" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I169" s="22"/>
+      <c r="I169" s="20"/>
       <c r="J169" s="9"/>
       <c r="K169" s="9"/>
       <c r="L169" s="9"/>
@@ -9321,7 +9348,7 @@
       <c r="O169" s="13"/>
     </row>
     <row r="170" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A170" s="19" t="s">
+      <c r="A170" s="21" t="s">
         <v>234</v>
       </c>
       <c r="B170" s="9" t="s">
@@ -9345,7 +9372,7 @@
       <c r="H170" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I170" s="22"/>
+      <c r="I170" s="20"/>
       <c r="J170" s="9"/>
       <c r="K170" s="9"/>
       <c r="L170" s="9"/>
@@ -9354,7 +9381,7 @@
       <c r="O170" s="13"/>
     </row>
     <row r="171" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A171" s="19" t="s">
+      <c r="A171" s="21" t="s">
         <v>235</v>
       </c>
       <c r="B171" s="9" t="s">
@@ -9378,7 +9405,7 @@
       <c r="H171" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I171" s="22"/>
+      <c r="I171" s="20"/>
       <c r="J171" s="9"/>
       <c r="K171" s="9"/>
       <c r="L171" s="9"/>
@@ -9387,7 +9414,7 @@
       <c r="O171" s="13"/>
     </row>
     <row r="172" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A172" s="19" t="s">
+      <c r="A172" s="21" t="s">
         <v>236</v>
       </c>
       <c r="B172" s="9" t="s">
@@ -9411,7 +9438,7 @@
       <c r="H172" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I172" s="22"/>
+      <c r="I172" s="20"/>
       <c r="J172" s="9"/>
       <c r="K172" s="9"/>
       <c r="L172" s="9"/>
@@ -9437,7 +9464,7 @@
       <c r="O173" s="26"/>
     </row>
     <row r="174" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A174" s="20" t="s">
+      <c r="A174" s="22" t="s">
         <v>237</v>
       </c>
       <c r="B174" s="9" t="s">
@@ -9461,7 +9488,7 @@
       <c r="H174" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I174" s="22"/>
+      <c r="I174" s="20"/>
       <c r="J174" s="9"/>
       <c r="K174" s="9"/>
       <c r="L174" s="9"/>
@@ -9470,7 +9497,7 @@
       <c r="O174" s="13"/>
     </row>
     <row r="175" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A175" s="20" t="s">
+      <c r="A175" s="22" t="s">
         <v>238</v>
       </c>
       <c r="B175" s="9" t="s">
@@ -9494,7 +9521,7 @@
       <c r="H175" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I175" s="22"/>
+      <c r="I175" s="20"/>
       <c r="J175" s="9"/>
       <c r="K175" s="9"/>
       <c r="L175" s="9"/>
@@ -9503,7 +9530,7 @@
       <c r="O175" s="13"/>
     </row>
     <row r="176" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A176" s="20" t="s">
+      <c r="A176" s="22" t="s">
         <v>239</v>
       </c>
       <c r="B176" s="9" t="s">
@@ -9527,7 +9554,7 @@
       <c r="H176" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I176" s="22"/>
+      <c r="I176" s="20"/>
       <c r="J176" s="9"/>
       <c r="K176" s="9"/>
       <c r="L176" s="9"/>
@@ -9536,7 +9563,7 @@
       <c r="O176" s="13"/>
     </row>
     <row r="177" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A177" s="20" t="s">
+      <c r="A177" s="22" t="s">
         <v>240</v>
       </c>
       <c r="B177" s="9" t="s">
@@ -9560,7 +9587,7 @@
       <c r="H177" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I177" s="22"/>
+      <c r="I177" s="20"/>
       <c r="J177" s="9"/>
       <c r="K177" s="9"/>
       <c r="L177" s="9"/>
@@ -9586,14 +9613,30 @@
       <c r="O178" s="26"/>
     </row>
     <row r="179" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A179" s="23"/>
-      <c r="B179" s="24"/>
-      <c r="C179" s="24"/>
-      <c r="D179" s="24"/>
-      <c r="E179" s="24"/>
-      <c r="F179" s="24"/>
-      <c r="G179" s="24"/>
-      <c r="H179" s="24"/>
+      <c r="A179" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C179" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D179" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E179" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F179" s="24">
+        <v>1</v>
+      </c>
+      <c r="G179" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H179" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="I179" s="25"/>
       <c r="J179" s="24"/>
       <c r="K179" s="24"/>
@@ -9603,14 +9646,30 @@
       <c r="O179" s="26"/>
     </row>
     <row r="180" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A180" s="23"/>
-      <c r="B180" s="24"/>
-      <c r="C180" s="24"/>
-      <c r="D180" s="24"/>
-      <c r="E180" s="24"/>
-      <c r="F180" s="24"/>
-      <c r="G180" s="24"/>
-      <c r="H180" s="24"/>
+      <c r="A180" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="B180" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C180" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D180" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E180" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F180" s="24">
+        <v>0</v>
+      </c>
+      <c r="G180" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H180" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="I180" s="25"/>
       <c r="J180" s="24"/>
       <c r="K180" s="24"/>
@@ -9620,14 +9679,30 @@
       <c r="O180" s="26"/>
     </row>
     <row r="181" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A181" s="23"/>
-      <c r="B181" s="24"/>
-      <c r="C181" s="24"/>
-      <c r="D181" s="24"/>
-      <c r="E181" s="24"/>
-      <c r="F181" s="24"/>
-      <c r="G181" s="24"/>
-      <c r="H181" s="24"/>
+      <c r="A181" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C181" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D181" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E181" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="F181" s="24">
+        <v>0</v>
+      </c>
+      <c r="G181" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H181" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="I181" s="25"/>
       <c r="J181" s="24"/>
       <c r="K181" s="24"/>
@@ -9637,14 +9712,30 @@
       <c r="O181" s="26"/>
     </row>
     <row r="182" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A182" s="23"/>
-      <c r="B182" s="24"/>
-      <c r="C182" s="24"/>
-      <c r="D182" s="24"/>
-      <c r="E182" s="24"/>
-      <c r="F182" s="24"/>
-      <c r="G182" s="24"/>
-      <c r="H182" s="24"/>
+      <c r="A182" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="B182" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C182" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D182" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E182" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F182" s="24">
+        <v>0</v>
+      </c>
+      <c r="G182" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H182" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="I182" s="25"/>
       <c r="J182" s="24"/>
       <c r="K182" s="24"/>
@@ -9654,14 +9745,30 @@
       <c r="O182" s="26"/>
     </row>
     <row r="183" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A183" s="23"/>
-      <c r="B183" s="24"/>
-      <c r="C183" s="24"/>
-      <c r="D183" s="24"/>
-      <c r="E183" s="24"/>
-      <c r="F183" s="24"/>
-      <c r="G183" s="24"/>
-      <c r="H183" s="24"/>
+      <c r="A183" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="B183" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C183" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D183" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E183" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F183" s="24">
+        <v>300</v>
+      </c>
+      <c r="G183" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H183" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="I183" s="25"/>
       <c r="J183" s="24"/>
       <c r="K183" s="24"/>
@@ -9671,14 +9778,30 @@
       <c r="O183" s="26"/>
     </row>
     <row r="184" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A184" s="23"/>
-      <c r="B184" s="24"/>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="24"/>
-      <c r="H184" s="24"/>
+      <c r="A184" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="B184" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C184" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D184" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E184" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F184" s="24">
+        <v>210</v>
+      </c>
+      <c r="G184" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H184" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="I184" s="25"/>
       <c r="J184" s="24"/>
       <c r="K184" s="24"/>
@@ -9688,14 +9811,30 @@
       <c r="O184" s="26"/>
     </row>
     <row r="185" s="14" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A185" s="23"/>
-      <c r="B185" s="24"/>
-      <c r="C185" s="24"/>
-      <c r="D185" s="24"/>
-      <c r="E185" s="24"/>
-      <c r="F185" s="24"/>
-      <c r="G185" s="24"/>
-      <c r="H185" s="24"/>
+      <c r="A185" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C185" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D185" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E185" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F185" s="24">
+        <v>0</v>
+      </c>
+      <c r="G185" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H185" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="I185" s="25"/>
       <c r="J185" s="24"/>
       <c r="K185" s="24"/>
@@ -9706,9 +9845,9 @@
     </row>
     <row r="186" s="14" customFormat="1" customHeight="1" spans="1:15">
       <c r="A186" s="23"/>
-      <c r="B186" s="24"/>
-      <c r="C186" s="24"/>
-      <c r="D186" s="24"/>
+      <c r="B186" s="9"/>
+      <c r="C186" s="9"/>
+      <c r="D186" s="9"/>
       <c r="E186" s="24"/>
       <c r="F186" s="24"/>
       <c r="G186" s="24"/>
@@ -9723,9 +9862,9 @@
     </row>
     <row r="187" s="14" customFormat="1" customHeight="1" spans="1:15">
       <c r="A187" s="23"/>
-      <c r="B187" s="24"/>
-      <c r="C187" s="24"/>
-      <c r="D187" s="24"/>
+      <c r="B187" s="9"/>
+      <c r="C187" s="9"/>
+      <c r="D187" s="9"/>
       <c r="E187" s="24"/>
       <c r="F187" s="24"/>
       <c r="G187" s="24"/>
@@ -11345,17 +11484,17 @@
       <c r="F282" s="15"/>
       <c r="G282" s="15"/>
       <c r="H282" s="15"/>
-      <c r="I282" s="29"/>
+      <c r="I282" s="28"/>
       <c r="J282" s="15"/>
       <c r="K282" s="15"/>
       <c r="L282" s="15"/>
       <c r="M282" s="15"/>
       <c r="N282" s="15"/>
-      <c r="O282" s="30"/>
-    </row>
-    <row r="283" customHeight="1" spans="1:9">
+      <c r="O282" s="29"/>
+    </row>
+    <row r="283" customHeight="1" spans="1:15">
       <c r="A283" s="16" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B283" s="9" t="s">
         <v>22</v>
@@ -11373,18 +11512,18 @@
         <v>600</v>
       </c>
       <c r="G283" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H283" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I283" s="22" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="284" customHeight="1" spans="1:9">
+        <v>250</v>
+      </c>
+      <c r="I283" s="20" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="284" customHeight="1" spans="1:15">
       <c r="A284" s="16" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B284" s="9" t="s">
         <v>22</v>
@@ -11402,18 +11541,18 @@
         <v>600</v>
       </c>
       <c r="G284" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H284" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I284" s="22" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="285" customHeight="1" spans="1:9">
+        <v>250</v>
+      </c>
+      <c r="I284" s="20" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="285" customHeight="1" spans="1:15">
       <c r="A285" s="16" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B285" s="9" t="s">
         <v>22</v>
@@ -11431,22 +11570,22 @@
         <v>600</v>
       </c>
       <c r="G285" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H285" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I285" s="22" t="s">
-        <v>248</v>
+        <v>250</v>
+      </c>
+      <c r="I285" s="20" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="289" customHeight="1" spans="1:9">
-      <c r="A289" s="28"/>
-      <c r="I289" s="22"/>
+      <c r="A289" s="30"/>
+      <c r="I289" s="20"/>
     </row>
     <row r="290" customHeight="1" spans="1:9">
-      <c r="A290" s="28" t="s">
-        <v>249</v>
+      <c r="A290" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="B290" s="9" t="s">
         <v>22</v>
@@ -11464,18 +11603,18 @@
         <v>1</v>
       </c>
       <c r="G290" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H290" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I290" s="22" t="s">
         <v>250</v>
       </c>
+      <c r="I290" s="20" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="291" customHeight="1" spans="1:9">
-      <c r="A291" s="28" t="s">
-        <v>251</v>
+      <c r="A291" s="30" t="s">
+        <v>258</v>
       </c>
       <c r="B291" s="9" t="s">
         <v>22</v>
@@ -11493,18 +11632,18 @@
         <v>1</v>
       </c>
       <c r="G291" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H291" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I291" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
+      </c>
+      <c r="I291" s="20" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="292" customHeight="1" spans="1:9">
-      <c r="A292" s="28" t="s">
-        <v>253</v>
+      <c r="A292" s="30" t="s">
+        <v>260</v>
       </c>
       <c r="B292" s="9" t="s">
         <v>22</v>
@@ -11522,21 +11661,21 @@
         <v>1</v>
       </c>
       <c r="G292" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H292" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I292" s="22" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="301" customHeight="1" spans="9:9">
-      <c r="I301" s="22"/>
+        <v>250</v>
+      </c>
+      <c r="I292" s="20" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="301" customHeight="1" spans="1:9">
+      <c r="I301" s="20"/>
     </row>
     <row r="302" customHeight="1" spans="1:9">
       <c r="A302" s="16" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B302" s="9" t="s">
         <v>22</v>
@@ -11554,18 +11693,18 @@
         <v>3800</v>
       </c>
       <c r="G302" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H302" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I302" s="22" t="s">
-        <v>256</v>
+        <v>250</v>
+      </c>
+      <c r="I302" s="20" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="303" customHeight="1" spans="1:9">
       <c r="A303" s="16" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B303" s="9" t="s">
         <v>22</v>
@@ -11583,18 +11722,18 @@
         <v>100</v>
       </c>
       <c r="G303" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H303" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I303" s="22" t="s">
-        <v>258</v>
+        <v>250</v>
+      </c>
+      <c r="I303" s="20" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="304" customHeight="1" spans="1:9">
       <c r="A304" s="16" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B304" s="9" t="s">
         <v>22</v>
@@ -11612,18 +11751,18 @@
         <v>0</v>
       </c>
       <c r="G304" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H304" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I304" s="22" t="s">
-        <v>260</v>
+        <v>250</v>
+      </c>
+      <c r="I304" s="20" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="305" customHeight="1" spans="1:9">
       <c r="A305" s="16" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B305" s="9" t="s">
         <v>22</v>
@@ -11641,18 +11780,18 @@
         <v>160</v>
       </c>
       <c r="G305" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H305" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I305" s="22" t="s">
-        <v>262</v>
+        <v>250</v>
+      </c>
+      <c r="I305" s="20" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="306" customHeight="1" spans="1:9">
       <c r="A306" s="16" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B306" s="9" t="s">
         <v>22</v>
@@ -11670,18 +11809,18 @@
         <v>140</v>
       </c>
       <c r="G306" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H306" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I306" s="22" t="s">
-        <v>264</v>
+        <v>250</v>
+      </c>
+      <c r="I306" s="20" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="307" customHeight="1" spans="1:9">
       <c r="A307" s="16" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B307" s="9" t="s">
         <v>22</v>
@@ -11699,18 +11838,18 @@
         <v>0</v>
       </c>
       <c r="G307" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H307" s="9" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="I307" s="31" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="310" customHeight="1" spans="1:8">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="310" customHeight="1" spans="1:9">
       <c r="A310" s="16" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B310" s="9" t="s">
         <v>22</v>
@@ -11728,15 +11867,15 @@
         <v>160</v>
       </c>
       <c r="G310" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H310" s="9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="311" customHeight="1" spans="1:8">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="311" customHeight="1" spans="1:9">
       <c r="A311" s="16" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B311" s="9" t="s">
         <v>22</v>
@@ -11754,15 +11893,15 @@
         <v>140</v>
       </c>
       <c r="G311" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H311" s="9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="313" customHeight="1" spans="1:8">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="313" customHeight="1" spans="1:9">
       <c r="A313" s="16" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B313" s="9" t="s">
         <v>22</v>
@@ -11780,15 +11919,15 @@
         <v>0</v>
       </c>
       <c r="G313" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H313" s="9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="314" customHeight="1" spans="1:8">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="314" customHeight="1" spans="1:9">
       <c r="A314" s="16" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B314" s="9" t="s">
         <v>22</v>
@@ -11806,15 +11945,15 @@
         <v>0</v>
       </c>
       <c r="G314" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H314" s="9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="315" customHeight="1" spans="1:8">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="315" customHeight="1" spans="1:9">
       <c r="A315" s="16" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B315" s="9" t="s">
         <v>22</v>
@@ -11832,15 +11971,15 @@
         <v>0</v>
       </c>
       <c r="G315" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H315" s="9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="316" customHeight="1" spans="1:8">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="316" customHeight="1" spans="1:9">
       <c r="A316" s="16" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B316" s="9" t="s">
         <v>22</v>
@@ -11858,15 +11997,15 @@
         <v>0</v>
       </c>
       <c r="G316" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H316" s="9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="318" customHeight="1" spans="1:8">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="318" customHeight="1" spans="1:9">
       <c r="A318" s="16" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B318" s="9" t="s">
         <v>22</v>
@@ -11884,15 +12023,15 @@
         <v>8600</v>
       </c>
       <c r="G318" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H318" s="9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="319" customHeight="1" spans="1:8">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="319" customHeight="1" spans="1:9">
       <c r="A319" s="16" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B319" s="9" t="s">
         <v>22</v>
@@ -11910,15 +12049,15 @@
         <v>9000</v>
       </c>
       <c r="G319" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H319" s="9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="320" customHeight="1" spans="1:8">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="320" customHeight="1" spans="1:9">
       <c r="A320" s="16" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B320" s="9" t="s">
         <v>22</v>
@@ -11936,15 +12075,15 @@
         <v>0</v>
       </c>
       <c r="G320" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H320" s="9" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="321" customHeight="1" spans="1:8">
       <c r="A321" s="16" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B321" s="9" t="s">
         <v>22</v>
@@ -11962,15 +12101,15 @@
         <v>0</v>
       </c>
       <c r="G321" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H321" s="9" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="323" customHeight="1" spans="1:8">
       <c r="A323" s="16" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B323" s="9" t="s">
         <v>22</v>
@@ -11988,15 +12127,15 @@
         <v>720</v>
       </c>
       <c r="G323" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H323" s="9" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="325" customHeight="1" spans="1:8">
       <c r="A325" s="16" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B325" s="9" t="s">
         <v>22</v>
@@ -12014,24 +12153,24 @@
         <v>60000</v>
       </c>
       <c r="G325" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H325" s="9" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B83 B85:B97 B99:B173 B174:B177 B178:B285 B289:B293 B296:B298 B301:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B83 B85:B97 B99:B285 B289:B293 B296:B298 B301:B1048576">
       <formula1>Config!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C83 C85:C97 C99:C173 C174:C177 C178:C285 C289:C293 C296:C298 C301:C1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C83 C85:C97 C99:C285 C289:C293 C296:C298 C301:C1048576">
       <formula1>Config!$B$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D83 D85:D97 D99:D173 D174:D177 D178:D285 D289:D293 D296:D298 D301:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D83 D85:D97 D99:D285 D289:D293 D296:D298 D301:D1048576">
       <formula1>Config!$C$2:$C$12</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E83 E85:E97 E99:E173 E174:E177 E178:E285 E289:E293 E296:E298 E301:E1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E83 E85:E97 E99:E285 E289:E293 E296:E298 E301:E1048576">
       <formula1>Config!$D$2:$D$15</formula1>
     </dataValidation>
   </dataValidations>
@@ -12044,19 +12183,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="20" customHeight="1" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.72380952380952" defaultRowHeight="20" customHeight="1" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="10.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="12.3636363636364" customWidth="1"/>
-    <col min="3" max="3" width="26.3636363636364" customWidth="1"/>
+    <col min="1" max="1" width="10.7238095238095" customWidth="1"/>
+    <col min="2" max="2" width="12.3619047619048" customWidth="1"/>
+    <col min="3" max="3" width="26.3619047619048" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="30.7272727272727" customWidth="1"/>
+    <col min="5" max="5" width="30.7238095238095" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="11" customFormat="1" customHeight="1" spans="1:6">
       <c r="A1" s="12" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>15</v>
@@ -12065,18 +12204,18 @@
         <v>13</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" s="7" customFormat="1" customHeight="1" spans="1:6">
       <c r="A2" s="13" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="9" t="s">
@@ -12098,23 +12237,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="20" customHeight="1" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="8.72380952380952" defaultRowHeight="20" customHeight="1" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.6727272727273" style="7" customWidth="1"/>
-    <col min="2" max="2" width="18.5090909090909" style="7" customWidth="1"/>
-    <col min="3" max="3" width="13.2545454545455" style="7" customWidth="1"/>
-    <col min="4" max="4" width="16.1181818181818" style="7" customWidth="1"/>
-    <col min="5" max="5" width="16.6909090909091" style="7" customWidth="1"/>
-    <col min="6" max="6" width="10.1909090909091" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="8.72727272727273" style="7"/>
+    <col min="1" max="1" width="13.6761904761905" style="7" customWidth="1"/>
+    <col min="2" max="2" width="18.5047619047619" style="7" customWidth="1"/>
+    <col min="3" max="3" width="13.2571428571429" style="7" customWidth="1"/>
+    <col min="4" max="4" width="16.1142857142857" style="7" customWidth="1"/>
+    <col min="5" max="5" width="16.6952380952381" style="7" customWidth="1"/>
+    <col min="6" max="6" width="10.1904761904762" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="8.72380952380952" style="7"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:6">
       <c r="A1" s="8" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>11</v>
@@ -12131,10 +12270,10 @@
     </row>
     <row r="2" customHeight="1" spans="1:6">
       <c r="A2" s="9" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>25</v>
@@ -12145,10 +12284,10 @@
     </row>
     <row r="3" customHeight="1" spans="1:6">
       <c r="A3" s="9" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>25</v>
@@ -12159,10 +12298,10 @@
     </row>
     <row r="4" customHeight="1" spans="1:6">
       <c r="A4" s="9" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>69</v>
@@ -12205,16 +12344,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="9.85454545454546" defaultRowHeight="20" customHeight="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.85714285714286" defaultRowHeight="20" customHeight="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="15.2545454545455" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.4272727272727" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7090909090909" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.7090909090909" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85454545454546" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.4272727272727" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.2181818181818" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.85454545454546" style="1"/>
+    <col min="1" max="1" width="15.2571428571429" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.4285714285714" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7047619047619" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.7047619047619" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85714285714286" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.4285714285714" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.2190476190476" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.85714285714286" style="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:7">
@@ -12225,16 +12364,16 @@
         <v>9</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>20</v>
@@ -12245,7 +12384,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>94</v>
@@ -12254,19 +12393,19 @@
         <v>69</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:7">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -12275,10 +12414,10 @@
         <v>25</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="G3" s="3"/>
     </row>
@@ -12286,13 +12425,13 @@
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -12301,13 +12440,13 @@
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -12316,13 +12455,13 @@
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -12331,13 +12470,13 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -12346,10 +12485,10 @@
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -12359,7 +12498,7 @@
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>34</v>
@@ -12372,10 +12511,10 @@
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -12385,10 +12524,10 @@
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -12398,16 +12537,16 @@
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
     </row>
-    <row r="14" customHeight="1" spans="4:4">
+    <row r="14" customHeight="1" spans="1:7">
       <c r="D14" s="6"/>
     </row>
   </sheetData>
